--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostAllocationExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostAllocationExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>核算期间</t>
   </si>
@@ -79,60 +79,187 @@
     <t>分摊重量</t>
   </si>
   <si>
+    <t>单位成本</t>
+  </si>
+  <si>
+    <t>总成本</t>
+  </si>
+  <si>
+    <t>期初签收</t>
+  </si>
+  <si>
+    <t>上月签收</t>
+  </si>
+  <si>
+    <t>本月签收</t>
+  </si>
+  <si>
+    <t>截止上月签收</t>
+  </si>
+  <si>
+    <t>截止本月签收</t>
+  </si>
+  <si>
+    <t>费用来源</t>
+  </si>
+  <si>
+    <t>费用分类</t>
+  </si>
+  <si>
+    <t>费用分摊方式</t>
+  </si>
+  <si>
+    <t>头程金额(总)</t>
+  </si>
+  <si>
+    <t>头程分摊金额</t>
+  </si>
+  <si>
+    <t>单个产品分摊</t>
+  </si>
+  <si>
+    <t>期初在途费用</t>
+  </si>
+  <si>
+    <t>期初暂估费用</t>
+  </si>
+  <si>
+    <t>冲期初在途费用</t>
+  </si>
+  <si>
+    <t>本期分摊费用</t>
+  </si>
+  <si>
+    <t>期末在途费用</t>
+  </si>
+  <si>
+    <t>期末暂估费用</t>
+  </si>
+  <si>
+    <t>分摊组织</t>
+  </si>
+  <si>
+    <t>{.reportPeriodStr}</t>
+  </si>
+  <si>
+    <t>{.accountPeriod}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.supplierName}</t>
+  </si>
+  <si>
+    <t>{.businessCode}</t>
+  </si>
+  <si>
+    <t>{.transportNo}</t>
+  </si>
+  <si>
     <t>{.sourceCode}</t>
   </si>
   <si>
-    <t>{.businessCode}</t>
+    <t>{.reconciliationMonthStr}</t>
+  </si>
+  <si>
+    <t>{.receiveTime}</t>
   </si>
   <si>
     <t>{.shopName}</t>
   </si>
   <si>
-    <t>{.warehouseName}</t>
+    <t>{.fromWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.toWarehouseName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.productName}</t>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.deliveryQty}</t>
+  </si>
+  <si>
+    <t>{.allocatedWeight}</t>
+  </si>
+  <si>
+    <t>{.productCost}</t>
+  </si>
+  <si>
+    <t>{.productTotalCost}</t>
   </si>
   <si>
     <t>{.initReceiveQty}</t>
   </si>
   <si>
+    <t>{.lastMonthReceiveQty}</t>
+  </si>
+  <si>
+    <t>{.currentMonthReceiveQty}</t>
+  </si>
+  <si>
+    <t>{.asLastMonthReceiveQty}</t>
+  </si>
+  <si>
+    <t>{.asCurrentMonthReceiveQty}</t>
+  </si>
+  <si>
+    <t>{.billSourceTypeName}</t>
+  </si>
+  <si>
+    <t>{.feeTypeName}</t>
+  </si>
+  <si>
+    <t>{.allocationTypeName}</t>
+  </si>
+  <si>
+    <t>{.amount}</t>
+  </si>
+  <si>
+    <t>{.allocatedAmount}</t>
+  </si>
+  <si>
+    <t>{.productAllocatedAmount}</t>
+  </si>
+  <si>
     <t>{.initTransitCost}</t>
   </si>
   <si>
-    <t>{.initTransitTariff}</t>
-  </si>
-  <si>
     <t>{.initEstimatedCost}</t>
   </si>
   <si>
-    <t>{.initEstimatedTariff}</t>
-  </si>
-  <si>
-    <t>{.weightAllocation}</t>
-  </si>
-  <si>
-    <t>{.productCost}</t>
-  </si>
-  <si>
-    <t>{.currency}</t>
+    <t>{.midPeriodTransitCost}</t>
+  </si>
+  <si>
+    <t>{.currentPeriodAllocatedCost}</t>
+  </si>
+  <si>
+    <t>{.endPeriodTransitCost}</t>
+  </si>
+  <si>
+    <t>{.endPeriodEstimatedCost}</t>
+  </si>
+  <si>
+    <t>{.orgName}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="0.000000_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -743,29 +870,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1079,27 +1209,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="14.375" customWidth="1"/>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="18.875" customWidth="1"/>
-    <col min="6" max="6" width="24.125" customWidth="1"/>
-    <col min="7" max="7" width="21.75" customWidth="1"/>
-    <col min="8" max="8" width="21.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.375" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
-    <col min="11" max="11" width="23.75" customWidth="1"/>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="5" max="5" width="8.875" customWidth="1"/>
+    <col min="6" max="6" width="12.125" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" customWidth="1"/>
+    <col min="10" max="10" width="10.125" customWidth="1"/>
+    <col min="11" max="11" width="19.625" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="17.375" customWidth="1"/>
-    <col min="14" max="14" width="15.625" customWidth="1"/>
+    <col min="13" max="13" width="8.5" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="15" width="9" style="2"/>
+    <col min="16" max="16" width="9" style="3"/>
+    <col min="17" max="17" width="9" style="4"/>
+    <col min="18" max="18" width="9" style="3"/>
+    <col min="19" max="23" width="9" style="2"/>
+    <col min="27" max="28" width="9" style="3"/>
+    <col min="29" max="29" width="9" style="4"/>
+    <col min="30" max="35" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:36">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1111,7 +1249,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1123,73 +1261,199 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>41</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>49</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostAllocationExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostAllocationExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>核算期间</t>
   </si>
@@ -76,13 +76,13 @@
     <t>发货数量</t>
   </si>
   <si>
-    <t>分摊重量</t>
-  </si>
-  <si>
-    <t>单位成本</t>
-  </si>
-  <si>
-    <t>总成本</t>
+    <t>分摊重量(kg)</t>
+  </si>
+  <si>
+    <t>单位成本(￥)</t>
+  </si>
+  <si>
+    <t>总成本(￥)</t>
   </si>
   <si>
     <t>期初签收</t>
@@ -109,34 +109,43 @@
     <t>费用分摊方式</t>
   </si>
   <si>
-    <t>头程金额(总)</t>
-  </si>
-  <si>
-    <t>头程分摊金额</t>
-  </si>
-  <si>
-    <t>单个产品分摊</t>
-  </si>
-  <si>
-    <t>期初在途费用</t>
-  </si>
-  <si>
-    <t>期初暂估费用</t>
-  </si>
-  <si>
-    <t>冲期初在途费用</t>
-  </si>
-  <si>
-    <t>本期分摊费用</t>
-  </si>
-  <si>
-    <t>期末在途费用</t>
-  </si>
-  <si>
-    <t>期末暂估费用</t>
-  </si>
-  <si>
-    <t>分摊组织</t>
+    <t>头程金额(总)(￥)</t>
+  </si>
+  <si>
+    <t>头程分摊金额(￥)</t>
+  </si>
+  <si>
+    <t>单个产品分摊(￥)</t>
+  </si>
+  <si>
+    <t>期初在途费用(￥)</t>
+  </si>
+  <si>
+    <t>期初暂估费用(￥)</t>
+  </si>
+  <si>
+    <t>冲期初在途费用(￥)</t>
+  </si>
+  <si>
+    <t>本期分摊费用(￥)</t>
+  </si>
+  <si>
+    <t>期末在途费用(￥)</t>
+  </si>
+  <si>
+    <t>期末暂估费用(￥)</t>
+  </si>
+  <si>
+    <t>分摊组织(￥)</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>更新人</t>
+  </si>
+  <si>
+    <t>更新时间</t>
   </si>
   <si>
     <t>{.reportPeriodStr}</t>
@@ -245,6 +254,15 @@
   </si>
   <si>
     <t>{.orgName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.updateUserName}</t>
+  </si>
+  <si>
+    <t>{.updateTime}</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1227,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AM2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
@@ -1236,7 +1254,7 @@
     <col min="30" max="35" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:39">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1345,115 +1363,133 @@
       <c r="AJ1" t="s">
         <v>35</v>
       </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:39">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="X2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Y2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Z2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AJ2" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostAllocationExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileCostAllocationExport.xlsx
@@ -196,7 +196,7 @@
     <t>{.allocatedWeight}</t>
   </si>
   <si>
-    <t>{.productCost}</t>
+    <t>{.productCostStr}</t>
   </si>
   <si>
     <t>{.productTotalCost}</t>
